--- a/test-data/subjects-sem6.xlsx
+++ b/test-data/subjects-sem6.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +418,9 @@
       <c r="F1" t="str">
         <v>electiveGroupId</v>
       </c>
+      <c r="G1" t="str">
+        <v>tcp</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -438,6 +441,9 @@
       <c r="F2" t="str">
         <v/>
       </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -458,6 +464,9 @@
       <c r="F3" t="str">
         <v/>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -478,6 +487,9 @@
       <c r="F4" t="str">
         <v/>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -498,6 +510,9 @@
       <c r="F5" t="str">
         <v/>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -518,6 +533,9 @@
       <c r="F6" t="str">
         <v/>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -538,6 +556,9 @@
       <c r="F7" t="str">
         <v/>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -558,6 +579,9 @@
       <c r="F8" t="str">
         <v/>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -578,6 +602,9 @@
       <c r="F9" t="str">
         <v/>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -598,6 +625,9 @@
       <c r="F10" t="str">
         <v/>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -618,6 +648,9 @@
       <c r="F11" t="str">
         <v/>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -638,6 +671,9 @@
       <c r="F12" t="str">
         <v/>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -658,6 +694,9 @@
       <c r="F13" t="str">
         <v/>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -678,6 +717,9 @@
       <c r="F14" t="str">
         <v/>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -698,6 +740,9 @@
       <c r="F15" t="str">
         <v/>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -718,6 +763,9 @@
       <c r="F16" t="str">
         <v/>
       </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -738,6 +786,9 @@
       <c r="F17" t="str">
         <v/>
       </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -758,6 +809,9 @@
       <c r="F18" t="str">
         <v/>
       </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -778,6 +832,9 @@
       <c r="F19" t="str">
         <v/>
       </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -798,6 +855,9 @@
       <c r="F20" t="str">
         <v/>
       </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -818,6 +878,9 @@
       <c r="F21" t="str">
         <v/>
       </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -838,6 +901,9 @@
       <c r="F22" t="str">
         <v/>
       </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -858,6 +924,9 @@
       <c r="F23" t="str">
         <v/>
       </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -878,6 +947,9 @@
       <c r="F24" t="str">
         <v/>
       </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -898,6 +970,9 @@
       <c r="F25" t="str">
         <v/>
       </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -918,6 +993,9 @@
       <c r="F26" t="str">
         <v/>
       </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -938,6 +1016,9 @@
       <c r="F27" t="str">
         <v/>
       </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -958,6 +1039,9 @@
       <c r="F28" t="str">
         <v/>
       </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -978,6 +1062,9 @@
       <c r="F29" t="str">
         <v/>
       </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -998,10 +1085,13 @@
       <c r="F30" t="str">
         <v/>
       </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G30"/>
   </ignoredErrors>
 </worksheet>
 </file>